--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487934_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487934_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7498</v>
+        <v>6.9817</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8028</v>
+        <v>5.475</v>
       </c>
       <c r="F2" t="n">
-        <v>1.947</v>
+        <v>1.5066</v>
       </c>
       <c r="G2" t="n">
         <v>3.4127</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4401</v>
+        <v>1.672</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2827</v>
+        <v>0.9549</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1574</v>
+        <v>0.7171</v>
       </c>
       <c r="V2" t="n">
         <v>2.1051</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4367</v>
+        <v>4.0947</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1692</v>
+        <v>3.062</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2675</v>
+        <v>1.0326</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6856</v>
@@ -688,13 +688,13 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1202</v>
+        <v>0.7782</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4005</v>
+        <v>0.2934</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7197</v>
+        <v>0.4848</v>
       </c>
       <c r="V3" t="n">
         <v>4.2102</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5968</v>
+        <v>3.9938</v>
       </c>
       <c r="E4" t="n">
-        <v>4.92</v>
+        <v>5.1996</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3232</v>
+        <v>-1.2058</v>
       </c>
       <c r="G4" t="n">
         <v>2.1618</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1031</v>
+        <v>0.5001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0619</v>
+        <v>0.3415</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0411</v>
+        <v>0.1586</v>
       </c>
       <c r="V4" t="n">
         <v>0.7076</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7207</v>
+        <v>3.3129</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2514</v>
+        <v>4.6381</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5308</v>
+        <v>-1.3253</v>
       </c>
       <c r="G5" t="n">
         <v>1.857</v>
@@ -844,13 +844,13 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3445</v>
+        <v>0.2478</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3791</v>
+        <v>0.0076</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0346</v>
+        <v>0.2401</v>
       </c>
       <c r="V5" t="n">
         <v>0.5838</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3111</v>
+        <v>3.1176</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1597</v>
+        <v>6.7607</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.8485</v>
+        <v>-3.643</v>
       </c>
       <c r="G6" t="n">
         <v>7.5374</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8912</v>
+        <v>-0.0847</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7053</v>
+        <v>-0.1043</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1859</v>
+        <v>0.0196</v>
       </c>
       <c r="V6" t="n">
         <v>-3.5026</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0261</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4104</v>
+        <v>1.8922</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4365</v>
+        <v>-1.0469</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5868</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9851</v>
+        <v>1.5374</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6017</v>
+        <v>-0.5903</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3172</v>
+        <v>2.2822</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.642</v>
+        <v>2.8399</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6752</v>
+        <v>-0.5576</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2696</v>
+        <v>-1.3351</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3431</v>
+        <v>-1.3025</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0735</v>
+        <v>-0.0326</v>
       </c>
       <c r="P7" t="n">
         <v>1.6649</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9479</v>
+        <v>-0.0155</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9068000000000001</v>
+        <v>-0.1819</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0411</v>
+        <v>0.1664</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5379</v>
+        <v>0.6077</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2912</v>
+        <v>-0.9462</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7533</v>
+        <v>1.5539</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9471000000000001</v>
+        <v>-1.5868</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5374</v>
+        <v>-0.9851</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5903</v>
+        <v>-0.6017</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2822</v>
+        <v>-1.3172</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8399</v>
+        <v>-0.642</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5576</v>
+        <v>-0.6752</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3351</v>
+        <v>-0.2696</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3025</v>
+        <v>-0.3431</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0326</v>
+        <v>0.0735</v>
       </c>
       <c r="P8" t="n">
         <v>1.6649</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3229</v>
+        <v>0.5296</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7829</v>
+        <v>0.371</v>
       </c>
       <c r="U8" t="n">
-        <v>0.46</v>
+        <v>0.1586</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2</v>
+        <v>0.2587</v>
       </c>
       <c r="E9" t="n">
         <v>-0.1574</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3574</v>
+        <v>0.4161</v>
       </c>
       <c r="G9" t="n">
         <v>0.2261</v>
@@ -1156,13 +1156,13 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4423</v>
+        <v>-0.3836</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8527</v>
+        <v>-0.4726</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1545</v>
+        <v>0.4759</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0072</v>
+        <v>-0.9485</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3263</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4671</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4443</v>
+        <v>-0.1228</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0228</v>
+        <v>0.0359</v>
       </c>
       <c r="V10" t="n">
         <v>1.3975</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.772</v>
+        <v>-1.6874</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6945</v>
+        <v>-1.7842</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0775</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.112</v>
+        <v>-1.4912</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4434</v>
+        <v>0.3988</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6686</v>
+        <v>-1.89</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3618</v>
+        <v>-0.7808</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2834</v>
+        <v>0.648</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0784</v>
+        <v>-1.4287</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4738</v>
+        <v>-0.7105</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7268</v>
+        <v>-0.2492</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.747</v>
+        <v>-0.4613</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0137</v>
+        <v>0.1794</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1924</v>
+        <v>0.0372</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2061</v>
+        <v>0.1423</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2629</v>
+        <v>-2.0347</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2128</v>
+        <v>-1.016</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0501</v>
+        <v>-1.0187</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4912</v>
+        <v>-1.112</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3988</v>
+        <v>-0.4434</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.89</v>
+        <v>-0.6686</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7808</v>
+        <v>0.3618</v>
       </c>
       <c r="K12" t="n">
-        <v>0.648</v>
+        <v>0.2834</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4287</v>
+        <v>0.0784</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7105</v>
+        <v>-1.4738</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2492</v>
+        <v>-0.7268</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4613</v>
+        <v>-0.747</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.396</v>
+        <v>-0.2765</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3915</v>
+        <v>-0.129</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0045</v>
+        <v>-0.1474</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.6915</v>
+        <v>19.0177</v>
       </c>
       <c r="E13" t="n">
-        <v>23.27369999999999</v>
+        <v>23.5997</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.582199999999999</v>
+        <v>-4.5823</v>
       </c>
       <c r="G13" t="n">
         <v>10.9402</v>
       </c>
       <c r="H13" t="n">
-        <v>3.816800000000001</v>
+        <v>3.816799999999999</v>
       </c>
       <c r="I13" t="n">
         <v>7.1233</v>
@@ -1447,7 +1447,7 @@
         <v>13.5148</v>
       </c>
       <c r="L13" t="n">
-        <v>9.062200000000001</v>
+        <v>9.062199999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-11.6367</v>
@@ -1468,13 +1468,13 @@
         <v>13.5278</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7336</v>
+        <v>3.059899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9455000000000002</v>
+        <v>1.2719</v>
       </c>
       <c r="U13" t="n">
-        <v>1.788</v>
+        <v>1.7881</v>
       </c>
       <c r="V13" t="n">
         <v>2.9365</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0885</v>
+        <v>1.4432</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9543</v>
+        <v>3.3476</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8659</v>
+        <v>-1.9044</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8491</v>
+        <v>-1.9946</v>
       </c>
       <c r="H14" t="n">
-        <v>3.117</v>
+        <v>-1.1855</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2679</v>
+        <v>-0.8091</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4823</v>
+        <v>0.5612</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0399</v>
+        <v>0.6967</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5576</v>
+        <v>-0.1355</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6331</v>
+        <v>-2.5558</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9228</v>
+        <v>-1.8823</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7103</v>
+        <v>-0.6735</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2081</v>
+        <v>1.2487</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R14" t="n">
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7825</v>
+        <v>-0.146</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0746</v>
+        <v>-0.5081</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7079</v>
+        <v>0.3621</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7513</v>
+        <v>2.3351</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3538</v>
+        <v>3.5026</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0836</v>
+        <v>1.2844</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8118</v>
+        <v>2.5613</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7282</v>
+        <v>-1.2769</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9946</v>
+        <v>1.8491</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1855</v>
+        <v>3.117</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8091</v>
+        <v>-1.2679</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5612</v>
+        <v>3.4823</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6967</v>
+        <v>4.0399</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1355</v>
+        <v>-0.5576</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5558</v>
+        <v>-1.6331</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8823</v>
+        <v>-0.9228</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6735</v>
+        <v>-0.7103</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R15" t="n">
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5056</v>
+        <v>0.9784</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0439</v>
+        <v>0.6815</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5383</v>
+        <v>0.2969</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3351</v>
+        <v>-1.7513</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5026</v>
+        <v>-0.3538</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4272</v>
+        <v>0.0105</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6908</v>
+        <v>-1.0697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2636</v>
+        <v>1.0802</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4609</v>
+        <v>1.7667</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7784</v>
+        <v>-0.3519</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6825</v>
+        <v>2.1186</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9426</v>
+        <v>2.3385</v>
       </c>
       <c r="K16" t="n">
-        <v>0.403</v>
+        <v>0.0443</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5396</v>
+        <v>2.2941</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5183</v>
+        <v>-0.5717</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3755</v>
+        <v>-0.3962</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1429</v>
+        <v>-0.1755</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6244</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.2487</v>
+        <v>-4.3705</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6113</v>
+        <v>-0.4264</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3229</v>
+        <v>-0.2052</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2884</v>
+        <v>-0.2211</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8751</v>
+        <v>1.1675</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7076</v>
+        <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6896</v>
+        <v>-0.759</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5926</v>
+        <v>-0.9051</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2822</v>
+        <v>0.1461</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9675</v>
+        <v>1.4609</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8337</v>
+        <v>0.7784</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1339</v>
+        <v>0.6825</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4002</v>
+        <v>0.9426</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3218</v>
+        <v>0.403</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0784</v>
+        <v>0.5396</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3677</v>
+        <v>0.5183</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1554</v>
+        <v>0.3755</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2123</v>
+        <v>0.1429</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1383</v>
+        <v>0.2796</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1924</v>
+        <v>0.1086</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3308</v>
+        <v>0.171</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.8751</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0141</v>
+        <v>-0.8643</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7126</v>
+        <v>0.2711</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6985</v>
+        <v>-1.1354</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7667</v>
+        <v>-0.9675</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3519</v>
+        <v>-0.8337</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1186</v>
+        <v>-0.1339</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3385</v>
+        <v>0.4002</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0443</v>
+        <v>0.3218</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2941</v>
+        <v>0.0784</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5717</v>
+        <v>-1.3677</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3962</v>
+        <v>-1.1554</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1755</v>
+        <v>-0.2123</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.4974</v>
+        <v>0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.3705</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.451</v>
+        <v>-0.313</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8482</v>
+        <v>-0.129</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6028</v>
+        <v>-0.184</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0011</v>
+        <v>-1.7178</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6674</v>
+        <v>1.7746</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6686</v>
+        <v>-3.4924</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8851</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0536</v>
+        <v>-0.7703</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5969</v>
+        <v>-0.4208</v>
       </c>
       <c r="V19" t="n">
         <v>0.3538</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4764</v>
+        <v>-2.4708</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0575</v>
+        <v>1.6775</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5338</v>
+        <v>-4.1483</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6269</v>
+        <v>-1.6011</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5969</v>
+        <v>0.7501</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2238</v>
+        <v>-2.3513</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7501</v>
+        <v>2.3425</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2812</v>
+        <v>3.0569</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4689</v>
+        <v>-0.7144</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1231</v>
+        <v>-3.9436</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8781</v>
+        <v>-2.3067</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.245</v>
+        <v>-1.6369</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8325</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6257</v>
+        <v>-0.4753</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1338</v>
+        <v>-0.4381</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4919</v>
+        <v>-0.0372</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6452</v>
+        <v>0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4776</v>
+        <v>0.8137</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.828</v>
+        <v>-2.4891</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4632</v>
+        <v>0.8431</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.2912</v>
+        <v>-3.3323</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6011</v>
+        <v>0.6269</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7501</v>
+        <v>-0.5969</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3513</v>
+        <v>1.2238</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3425</v>
+        <v>3.7501</v>
       </c>
       <c r="K21" t="n">
-        <v>3.0569</v>
+        <v>1.2812</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7144</v>
+        <v>2.4689</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.9436</v>
+        <v>-3.1231</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3067</v>
+        <v>-1.8781</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6369</v>
+        <v>-1.245</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6244</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8325</v>
+        <v>-0.6384</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6524</v>
+        <v>-0.3481</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.18</v>
+        <v>-0.2903</v>
       </c>
       <c r="V21" t="n">
-        <v>0.23</v>
+        <v>-1.6452</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8137</v>
+        <v>-0.4776</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4876</v>
+        <v>-3.9495</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1864</v>
+        <v>-0.2422</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.674</v>
+        <v>-3.7073</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6936</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3517</v>
+        <v>-0.1103</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3882</v>
+        <v>-0.0405</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0365</v>
+        <v>-0.0698</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5213</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6185</v>
+        <v>-4.0176</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1549</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4635</v>
+        <v>-3.2913</v>
       </c>
       <c r="G23" t="n">
         <v>-2.654</v>
@@ -2248,13 +2248,13 @@
         <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.67</v>
+        <v>-0.0692</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6524</v>
+        <v>-0.2238</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0176</v>
+        <v>0.1546</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3351</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.321</v>
+        <v>-4.4471</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5927</v>
+        <v>-2.9498</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7283</v>
+        <v>-1.4974</v>
       </c>
       <c r="G24" t="n">
         <v>-6.8481</v>
@@ -2326,13 +2326,13 @@
         <v>1.8731</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2024</v>
+        <v>-0.3285</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9786</v>
+        <v>-0.3357</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2237</v>
+        <v>0.0072</v>
       </c>
       <c r="V24" t="n">
         <v>2.1051</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.6914</v>
+        <v>-17.9771</v>
       </c>
       <c r="E25" t="n">
-        <v>4.582200000000001</v>
+        <v>4.582099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-23.2736</v>
+        <v>-22.5594</v>
       </c>
       <c r="G25" t="n">
         <v>-10.9404</v>
@@ -2404,19 +2404,19 @@
         <v>11.4465</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.7336</v>
+        <v>-2.0194</v>
       </c>
       <c r="T25" t="n">
         <v>-1.7879</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9455999999999999</v>
+        <v>-0.2314</v>
       </c>
       <c r="V25" t="n">
         <v>-2.936500000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>8.261100000000001</v>
+        <v>8.261099999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-11.1977</v>
